--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="265">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -414,9 +414,6 @@
     <t>iheAntigenDose</t>
   </si>
   <si>
-    <t xml:space="preserve">Conformité Antigen Dose (IHE PCC) </t>
-  </si>
-  <si>
     <t>Conformité Antigen Dose (IHE PCC)</t>
   </si>
   <si>
@@ -460,9 +457,6 @@
   </si>
   <si>
     <t>frDoseAntigene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conformité FR-Dose-antigene (CI-SIS) </t>
   </si>
   <si>
     <t>Conformité FR-Dose-antigene (CI-SIS)</t>
@@ -2373,7 +2367,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2444,10 +2438,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2545,10 +2539,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2648,10 +2642,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2751,10 +2745,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2783,7 +2777,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2795,7 +2789,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -2854,10 +2848,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2957,13 +2951,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -2988,10 +2982,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3062,10 +3056,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3163,10 +3157,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3266,10 +3260,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3369,10 +3363,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3401,7 +3395,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3413,7 +3407,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3472,10 +3466,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3575,10 +3569,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3592,7 +3586,7 @@
         <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -3612,7 +3606,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>75</v>
@@ -3634,7 +3628,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -3652,7 +3646,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3672,10 +3666,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3689,7 +3683,7 @@
         <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>75</v>
@@ -3712,7 +3706,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -3731,7 +3725,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -3749,7 +3743,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3769,10 +3763,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3786,7 +3780,7 @@
         <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>75</v>
@@ -3798,10 +3792,10 @@
         <v>96</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3852,7 +3846,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -3872,10 +3866,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3898,7 +3892,7 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -3927,11 +3921,11 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -3949,7 +3943,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -3969,10 +3963,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4048,7 +4042,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4068,10 +4062,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4094,7 +4088,7 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -4147,7 +4141,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4167,10 +4161,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4226,7 +4220,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4244,7 +4238,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4264,10 +4258,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4290,7 +4284,7 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -4343,7 +4337,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4363,10 +4357,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4389,7 +4383,7 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -4418,11 +4412,11 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -4440,7 +4434,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4460,10 +4454,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4486,7 +4480,7 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -4539,7 +4533,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4559,10 +4553,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4585,7 +4579,7 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -4614,11 +4608,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -4636,7 +4630,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -4656,10 +4650,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4682,7 +4676,7 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -4711,11 +4705,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -4733,7 +4727,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -4753,10 +4747,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4779,10 +4773,10 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -4834,7 +4828,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -4854,10 +4848,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4955,17 +4949,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>76</v>
@@ -4987,7 +4981,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5038,7 +5032,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5058,17 +5052,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>76</v>
@@ -5086,11 +5080,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5141,7 +5135,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5161,17 +5155,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5189,11 +5183,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5244,7 +5238,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5264,10 +5258,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5294,12 +5288,12 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5325,7 +5319,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -5343,7 +5337,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5363,17 +5357,17 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>81</v>
@@ -5391,11 +5385,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5446,7 +5440,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5466,17 +5460,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>81</v>
@@ -5494,11 +5488,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5549,7 +5543,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5569,17 +5563,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -5597,11 +5591,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5652,7 +5646,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -5672,17 +5666,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -5700,11 +5694,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5755,7 +5749,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -5775,10 +5769,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5801,7 +5795,7 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -5854,7 +5848,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -5874,10 +5868,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5900,7 +5894,7 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -5953,7 +5947,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -5973,10 +5967,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5999,7 +5993,7 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6028,11 +6022,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6050,7 +6044,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6070,10 +6064,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6096,13 +6090,13 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6153,7 +6147,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6173,10 +6167,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6274,10 +6268,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6375,10 +6369,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6476,10 +6470,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6577,10 +6571,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6680,10 +6674,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6783,10 +6777,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6886,10 +6880,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6989,10 +6983,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7090,10 +7084,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7127,7 +7121,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7149,7 +7143,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -7167,7 +7161,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7187,10 +7181,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7213,7 +7207,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7266,7 +7260,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7286,10 +7280,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7312,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7365,7 +7359,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7385,10 +7379,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7411,7 +7405,7 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7464,7 +7458,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7484,10 +7478,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7510,7 +7504,7 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7563,7 +7557,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7583,10 +7577,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7609,7 +7603,7 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7662,7 +7656,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -7682,10 +7676,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7708,7 +7702,7 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7761,7 +7755,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -7781,10 +7775,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7807,7 +7801,7 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7860,7 +7854,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -7880,10 +7874,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7906,7 +7900,7 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -7959,7 +7953,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -7979,10 +7973,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8005,7 +7999,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8058,7 +8052,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8078,10 +8072,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8104,7 +8098,7 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8157,7 +8151,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8177,10 +8171,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8203,7 +8197,7 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8256,7 +8250,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
